--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488134_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488134_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.545</v>
+        <v>2.4749</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8074</v>
+        <v>3.1559</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2624</v>
+        <v>-0.681</v>
       </c>
       <c r="G2" t="n">
         <v>1.2286</v>
@@ -610,13 +610,13 @@
         <v>2.9646</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5365</v>
+        <v>-0.6065</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5931</v>
+        <v>-0.2446</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0567</v>
+        <v>-0.3619</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. GALIANO AVILA</t>
+          <t>T. PERRY II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0719</v>
+        <v>0.7599</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7771</v>
+        <v>3.1676</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7052</v>
+        <v>-2.4076</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.1999</v>
+        <v>0.9032</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6848</v>
+        <v>0.1723</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.8847</v>
+        <v>0.7309</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6939</v>
+        <v>3.072</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1809</v>
+        <v>0.6133</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.487</v>
+        <v>2.4587</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.8938</v>
+        <v>-2.1688</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4961</v>
+        <v>-0.441</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.3977</v>
+        <v>-1.7278</v>
       </c>
       <c r="P3" t="n">
-        <v>2.2234</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1853</v>
+        <v>-2.9646</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4087</v>
+        <v>2.9646</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6772</v>
+        <v>-1.6539</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2684</v>
+        <v>-1.0309</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5911999999999999</v>
+        <v>-0.623</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6289</v>
+        <v>1.5106</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>4.091</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6289</v>
+        <v>-2.5804</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. CISSE</t>
+          <t>S. CASAS GARCÍA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6542</v>
+        <v>0.3221</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4152</v>
+        <v>0.3221</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.761</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0994</v>
+        <v>0.3221</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8535</v>
+        <v>0.3221</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.7541</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9418</v>
+        <v>0.3221</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5933</v>
+        <v>0.3221</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3484</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.8424</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7398</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.1026</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.891</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>4.0763</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8272</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7822</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0451</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1967</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>3.1466</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.9498</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. CASAS GARCÍA</t>
+          <t>S. CISSE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3221</v>
+        <v>0.315</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3221</v>
+        <v>2.4699</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-2.1549</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3221</v>
+        <v>0.0994</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3221</v>
+        <v>1.8535</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-1.7541</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3221</v>
+        <v>3.9418</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3221</v>
+        <v>2.5933</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.3484</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-3.8424</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.7398</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-3.1026</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.891</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>4.0763</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-1.1664</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.7274</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.439</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.1967</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.1466</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.9498</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. PERRY II</t>
+          <t>S. GALIANO AVILA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2943</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7758</v>
+        <v>0.6999</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.4815</v>
+        <v>-0.6313</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9032</v>
+        <v>-1.1999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1723</v>
+        <v>0.6848</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7309</v>
+        <v>-1.8847</v>
       </c>
       <c r="J6" t="n">
-        <v>3.072</v>
+        <v>0.6939</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6133</v>
+        <v>1.1809</v>
       </c>
       <c r="L6" t="n">
-        <v>2.4587</v>
+        <v>-0.487</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.1688</v>
+        <v>-1.8938</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.441</v>
+        <v>-0.4961</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.7278</v>
+        <v>-1.3977</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.2234</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9646</v>
+        <v>-0.1853</v>
       </c>
       <c r="R6" t="n">
-        <v>2.9646</v>
+        <v>2.4087</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.1195</v>
+        <v>-0.3261</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.4226</v>
+        <v>0.1912</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6969</v>
+        <v>-0.5173</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5106</v>
+        <v>-0.6289</v>
       </c>
       <c r="W6" t="n">
-        <v>4.091</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.5804</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9752999999999999</v>
+        <v>-0.8035</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1974</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7779</v>
+        <v>-0.704</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9151</v>
@@ -1000,13 +1000,13 @@
         <v>0.3706</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4308</v>
+        <v>-0.259</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2189</v>
+        <v>-0.1209</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2119</v>
+        <v>-0.138</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1291</v>
+        <v>-1.2013</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5665</v>
+        <v>-0.8603</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5625</v>
+        <v>-0.341</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0525</v>
@@ -1078,13 +1078,13 @@
         <v>1.4823</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.336</v>
+        <v>-0.4082</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0386</v>
+        <v>-0.2552</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3746</v>
+        <v>-0.153</v>
       </c>
       <c r="V8" t="n">
         <v>0.63</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7513</v>
+        <v>-1.5789</v>
       </c>
       <c r="E9" t="n">
         <v>-0.0954</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6559</v>
+        <v>-1.4835</v>
       </c>
       <c r="G9" t="n">
         <v>0.3051</v>
@@ -1156,13 +1156,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9757</v>
+        <v>-0.8033</v>
       </c>
       <c r="T9" t="n">
         <v>-0.3071</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6685</v>
+        <v>-0.4962</v>
       </c>
       <c r="V9" t="n">
         <v>-1.6365</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7586</v>
+        <v>-1.7039</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0547</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>-1.7039</v>
@@ -1234,10 +1234,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1853</v>
+        <v>-0.1306</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0547</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>-0.1306</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2347</v>
+        <v>-2.2839</v>
       </c>
       <c r="E11" t="n">
         <v>-1.7571</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4776</v>
+        <v>-0.5269</v>
       </c>
       <c r="G11" t="n">
         <v>-2.2495</v>
@@ -1312,13 +1312,13 @@
         <v>0.7411</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3487</v>
+        <v>-0.3979</v>
       </c>
       <c r="T11" t="n">
         <v>-0.1977</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.151</v>
+        <v>-0.2002</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3777</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.47</v>
+        <v>-3.5143</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0803</v>
+        <v>-0.9276</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3897</v>
+        <v>-2.5867</v>
       </c>
       <c r="G12" t="n">
         <v>-1.2778</v>
@@ -1390,13 +1390,13 @@
         <v>1.4823</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5442</v>
+        <v>-0.5885</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7237</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1795</v>
+        <v>-0.0174</v>
       </c>
       <c r="V12" t="n">
         <v>-2.2038</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.8339</v>
+        <v>-4.2638</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.7987</v>
+        <v>-3.4502</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0352</v>
+        <v>-0.8136</v>
       </c>
       <c r="G13" t="n">
         <v>-3.3815</v>
@@ -1468,13 +1468,13 @@
         <v>2.2234</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3047</v>
+        <v>-0.7346</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.669</v>
+        <v>-0.3205</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6357</v>
+        <v>-0.4141</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2594</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.4662</v>
+        <v>-5.0487</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.7594</v>
+        <v>-2.5636</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.7067</v>
+        <v>-2.4851</v>
       </c>
       <c r="G14" t="n">
         <v>-3.4257</v>
@@ -1546,13 +1546,13 @@
         <v>2.0382</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8481</v>
+        <v>-1.4307</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9637</v>
+        <v>-0.7679</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8844</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3777</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-16.7316</v>
+        <v>-16.4578</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2119000000000022</v>
+        <v>0.06170000000000053</v>
       </c>
       <c r="F15" t="n">
         <v>-16.5195</v>
@@ -1597,7 +1597,7 @@
         <v>-14.9378</v>
       </c>
       <c r="J15" t="n">
-        <v>8.871900000000002</v>
+        <v>8.871899999999998</v>
       </c>
       <c r="K15" t="n">
         <v>8.181899999999999</v>
@@ -1615,7 +1615,7 @@
         <v>-15.6277</v>
       </c>
       <c r="P15" t="n">
-        <v>7.4115</v>
+        <v>7.411499999999999</v>
       </c>
       <c r="Q15" t="n">
         <v>-13.8965</v>
@@ -1624,13 +1624,13 @@
         <v>21.308</v>
       </c>
       <c r="S15" t="n">
-        <v>-8.779500000000001</v>
+        <v>-8.505700000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-4.6257</v>
+        <v>-4.3521</v>
       </c>
       <c r="U15" t="n">
-        <v>-4.1537</v>
+        <v>-4.153499999999999</v>
       </c>
       <c r="V15" t="n">
         <v>-4.72</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.2542</v>
+        <v>7.2445</v>
       </c>
       <c r="E16" t="n">
         <v>8.266400000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0122</v>
+        <v>-1.0219</v>
       </c>
       <c r="G16" t="n">
         <v>3.4628</v>
@@ -1702,13 +1702,13 @@
         <v>1.4823</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6089</v>
+        <v>1.5992</v>
       </c>
       <c r="T16" t="n">
         <v>0.8891</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7197</v>
+        <v>0.71</v>
       </c>
       <c r="V16" t="n">
         <v>4.406</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.5259</v>
+        <v>6.2877</v>
       </c>
       <c r="E17" t="n">
-        <v>5.9022</v>
+        <v>5.8043</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6236</v>
+        <v>0.4834</v>
       </c>
       <c r="G17" t="n">
         <v>0.1937</v>
@@ -1780,13 +1780,13 @@
         <v>1.8529</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3142</v>
+        <v>1.076</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3756</v>
+        <v>0.2776</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9386</v>
+        <v>0.7983</v>
       </c>
       <c r="V17" t="n">
         <v>4.0915</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.9793</v>
+        <v>4.4731</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2154</v>
+        <v>1.6278</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7639</v>
+        <v>2.8453</v>
       </c>
       <c r="G18" t="n">
         <v>2.6799</v>
@@ -1858,13 +1858,13 @@
         <v>1.8529</v>
       </c>
       <c r="S18" t="n">
-        <v>1.9506</v>
+        <v>1.4444</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0831</v>
+        <v>0.4956</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8675</v>
+        <v>0.9488</v>
       </c>
       <c r="V18" t="n">
         <v>2.2016</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. GARCIA FERNANDEZ</t>
+          <t>V. PIETUKHOV</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.9379</v>
+        <v>3.5665</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4528</v>
+        <v>2.5142</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4851</v>
+        <v>1.0524</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2483</v>
+        <v>2.705</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3707</v>
+        <v>-0.3992</v>
       </c>
       <c r="I19" t="n">
-        <v>1.619</v>
+        <v>3.1042</v>
       </c>
       <c r="J19" t="n">
-        <v>0.138</v>
+        <v>2.6034</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5669999999999999</v>
+        <v>0.0215</v>
       </c>
       <c r="L19" t="n">
-        <v>0.705</v>
+        <v>2.5819</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1103</v>
+        <v>0.1016</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8037</v>
+        <v>-0.4207</v>
       </c>
       <c r="O19" t="n">
-        <v>0.914</v>
+        <v>0.5223</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7411</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7411</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5783</v>
+        <v>0.2316</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6303</v>
+        <v>-0.0892</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9481000000000001</v>
+        <v>0.3208</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.63</v>
+        <v>0.63</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3155</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3144</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V. PIETUKHOV</t>
+          <t>M. GARCIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.9377</v>
+        <v>2.0628</v>
       </c>
       <c r="E20" t="n">
-        <v>2.2204</v>
+        <v>0.7673</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7174</v>
+        <v>1.2956</v>
       </c>
       <c r="G20" t="n">
-        <v>2.705</v>
+        <v>0.2483</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3992</v>
+        <v>-1.3707</v>
       </c>
       <c r="I20" t="n">
-        <v>3.1042</v>
+        <v>1.619</v>
       </c>
       <c r="J20" t="n">
-        <v>2.6034</v>
+        <v>0.138</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0215</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>2.5819</v>
+        <v>0.705</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1016</v>
+        <v>0.1103</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4207</v>
+        <v>-0.8037</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5223</v>
+        <v>0.914</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.7411</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.7411</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3972</v>
+        <v>1.7033</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.383</v>
+        <v>0.9448</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0142</v>
+        <v>0.7585</v>
       </c>
       <c r="V20" t="n">
-        <v>0.63</v>
+        <v>-0.63</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
       <c r="X20" t="n">
-        <v>0.63</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1854</v>
+        <v>0.0468</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9915</v>
+        <v>0.6978</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8061</v>
+        <v>-0.6509</v>
       </c>
       <c r="G21" t="n">
         <v>0.9143</v>
@@ -2092,13 +2092,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9006</v>
+        <v>0.762</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7287</v>
+        <v>0.4349</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1718</v>
+        <v>0.327</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2589</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1761</v>
+        <v>-0.0044</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.08799999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0882</v>
+        <v>-0.0143</v>
       </c>
       <c r="G22" t="n">
         <v>0.1985</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0602</v>
+        <v>0.1116</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1094</v>
+        <v>-0.0115</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0492</v>
+        <v>0.1231</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3144</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.146</v>
+        <v>-0.3855</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0352</v>
+        <v>-0.9372</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1108</v>
+        <v>0.5517</v>
       </c>
       <c r="G23" t="n">
         <v>-0.2125</v>
@@ -2248,13 +2248,13 @@
         <v>2.0382</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1047</v>
+        <v>0.8652</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0174</v>
+        <v>0.1154</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0873</v>
+        <v>0.7498</v>
       </c>
       <c r="V23" t="n">
         <v>0.6294</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. TOURE</t>
+          <t>P. HEPBURN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.6172</v>
+        <v>-1.2069</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7026</v>
+        <v>-0.4431</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3198</v>
+        <v>-0.7638</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2698</v>
+        <v>1.0033</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.17</v>
+        <v>-2.2162</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0998</v>
+        <v>3.2196</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5422</v>
+        <v>2.0586</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3348</v>
+        <v>-1.3836</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2074</v>
+        <v>3.4421</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.8120000000000001</v>
+        <v>-1.0552</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5048</v>
+        <v>-0.8327</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3071</v>
+        <v>-0.2226</v>
       </c>
       <c r="P24" t="n">
-        <v>0.3706</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3706</v>
+        <v>2.2234</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4847</v>
+        <v>0.8633</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1604</v>
+        <v>0.2776</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3243</v>
+        <v>0.5857</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.2027</v>
+        <v>-2.5177</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.2027</v>
+        <v>-2.5177</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. ALEMAN ROMERA</t>
+          <t>A. TOURE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.5626</v>
+        <v>-1.6092</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.5884</v>
+        <v>0.6047</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0258</v>
+        <v>-2.2139</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.2799</v>
+        <v>-0.2698</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.7252</v>
+        <v>-0.17</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4453</v>
+        <v>-0.0998</v>
       </c>
       <c r="J25" t="n">
-        <v>1.4655</v>
+        <v>0.5422</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.6401</v>
+        <v>0.3348</v>
       </c>
       <c r="L25" t="n">
-        <v>2.1056</v>
+        <v>0.2074</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.7454</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.0851</v>
+        <v>-0.5048</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.6603</v>
+        <v>-0.3071</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.7793</v>
+        <v>0.3706</v>
       </c>
       <c r="Q25" t="n">
-        <v>-5.5586</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.7793</v>
+        <v>0.3706</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8115</v>
+        <v>0.4928</v>
       </c>
       <c r="T25" t="n">
-        <v>0.5609</v>
+        <v>0.0625</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2507</v>
+        <v>0.4303</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.315</v>
+        <v>-2.2027</v>
       </c>
       <c r="W25" t="n">
-        <v>0.9439</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2589</v>
+        <v>-2.2027</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>P. HEPBURN</t>
+          <t>A. ALEMAN ROMERA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.5871</v>
+        <v>-1.7856</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.5203</v>
+        <v>-2.3925</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.0667</v>
+        <v>0.607</v>
       </c>
       <c r="G26" t="n">
-        <v>1.0033</v>
+        <v>-0.2799</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.2162</v>
+        <v>-1.7252</v>
       </c>
       <c r="I26" t="n">
-        <v>3.2196</v>
+        <v>1.4453</v>
       </c>
       <c r="J26" t="n">
-        <v>2.0586</v>
+        <v>1.4655</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.3836</v>
+        <v>-0.6401</v>
       </c>
       <c r="L26" t="n">
-        <v>3.4421</v>
+        <v>2.1056</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.0552</v>
+        <v>-1.7454</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.8327</v>
+        <v>-1.0851</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.2226</v>
+        <v>-0.6603</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-2.7793</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.7793</v>
+        <v>-5.5586</v>
       </c>
       <c r="R26" t="n">
-        <v>2.2234</v>
+        <v>2.7793</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5168</v>
+        <v>1.5886</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.7996</v>
+        <v>0.7567</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2828</v>
+        <v>0.8319</v>
       </c>
       <c r="V26" t="n">
-        <v>-2.5177</v>
+        <v>-0.315</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>0.9439</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.5177</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>16.7314</v>
+        <v>18.6898</v>
       </c>
       <c r="E27" t="n">
-        <v>16.5194</v>
+        <v>16.5197</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2120000000000009</v>
+        <v>2.170599999999999</v>
       </c>
       <c r="G27" t="n">
         <v>10.6436</v>
@@ -2545,10 +2545,10 @@
         <v>-8.8719</v>
       </c>
       <c r="N27" t="n">
-        <v>-8.181799999999999</v>
+        <v>-8.181800000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.6898999999999997</v>
+        <v>-0.6899</v>
       </c>
       <c r="P27" t="n">
         <v>-7.4116</v>
@@ -2560,13 +2560,13 @@
         <v>13.8966</v>
       </c>
       <c r="S27" t="n">
-        <v>8.779300000000001</v>
+        <v>10.738</v>
       </c>
       <c r="T27" t="n">
         <v>4.1535</v>
       </c>
       <c r="U27" t="n">
-        <v>4.625800000000001</v>
+        <v>6.5842</v>
       </c>
       <c r="V27" t="n">
         <v>4.719799999999998</v>
@@ -2575,7 +2575,7 @@
         <v>14.1586</v>
       </c>
       <c r="X27" t="n">
-        <v>-9.438599999999999</v>
+        <v>-9.438600000000001</v>
       </c>
     </row>
   </sheetData>
